--- a/output/pdf_financials_xlsx/NGEX.xlsx
+++ b/output/pdf_financials_xlsx/NGEX.xlsx
@@ -841,25 +841,25 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>6.336936</v>
+        <v>-6.336936</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>5.306919</v>
+        <v>-5.306919</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5.456734</v>
+        <v>-5.456734</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>32.415262</v>
+        <v>-32.415262</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>37.831493</v>
+        <v>-37.604891</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>64.14661599999999</v>
+        <v>-63.047008</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>124.199249</v>
+        <v>-122.472475</v>
       </c>
     </row>
     <row r="17">
@@ -981,25 +981,25 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>6.336936</v>
+        <v>-6.336936</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>5.306919</v>
+        <v>-5.306919</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5.456734</v>
+        <v>-5.456734</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>32.415262</v>
+        <v>-32.415262</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>37.718192</v>
+        <v>-37.718192</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>63.596812</v>
+        <v>-63.596812</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>123.335862</v>
+        <v>-123.335862</v>
       </c>
     </row>
     <row r="21">
@@ -1065,25 +1065,25 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>6.336936</v>
+        <v>-6.336936</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>5.306919</v>
+        <v>-5.306919</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>5.456734</v>
+        <v>-5.456734</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>32.415262</v>
+        <v>-32.415262</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>37.718192</v>
+        <v>-37.718192</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>63.596812</v>
+        <v>-63.596812</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>123.335862</v>
+        <v>-123.335862</v>
       </c>
     </row>
     <row r="24">
@@ -1149,25 +1149,25 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>126.73872</v>
+        <v>-126.73872</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>132.672975</v>
+        <v>-132.672975</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>136.41835</v>
+        <v>-136.41835</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>162.07631</v>
+        <v>-162.07631</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>179.610438</v>
+        <v>-179.610438</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>192.717612</v>
+        <v>-192.717612</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>202.189938</v>
+        <v>-202.189938</v>
       </c>
     </row>
     <row r="27">
@@ -1177,25 +1177,25 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>6.336936</v>
+        <v>-6.336936</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>5.306919</v>
+        <v>-5.306919</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>5.456734</v>
+        <v>-5.456734</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>32.415262</v>
+        <v>-32.415262</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>37.831493</v>
+        <v>-37.604891</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>64.14661599999999</v>
+        <v>-63.047008</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>124.199249</v>
+        <v>-122.472475</v>
       </c>
     </row>
     <row r="28">
@@ -1233,25 +1233,25 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>6.345918</v>
+        <v>-6.327954</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>5.309862</v>
+        <v>-5.303976</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>5.465545</v>
+        <v>-5.447923</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>32.427537</v>
+        <v>-32.402987</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>37.848724</v>
+        <v>-37.58766</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>64.204808</v>
+        <v>-62.988816</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>124.26992</v>
+        <v>-122.401804</v>
       </c>
     </row>
     <row r="30">
@@ -1303,25 +1303,25 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.2994885768848721</v>
+        <v>-0.3012932546460512</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.8571052290583809</v>
+        <v>-0.8720540711464055</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.6951628185771075</v>
+        <v>-0.7049641154063393</v>
       </c>
     </row>
     <row r="32">
@@ -10442,19 +10442,19 @@
         </is>
       </c>
       <c r="G127" s="5" t="n">
-        <v>5.456734</v>
+        <v>-5.456734</v>
       </c>
       <c r="H127" s="5" t="n">
-        <v>32.415262</v>
+        <v>-32.415262</v>
       </c>
       <c r="I127" s="5" t="n">
-        <v>37.718192</v>
+        <v>-37.718192</v>
       </c>
       <c r="J127" s="5" t="n">
-        <v>63.596812</v>
+        <v>-63.596812</v>
       </c>
       <c r="K127" s="5" t="n">
-        <v>123.335862</v>
+        <v>-123.335862</v>
       </c>
     </row>
     <row r="128">
@@ -11478,10 +11478,10 @@
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>6.336936</v>
+        <v>-6.336936</v>
       </c>
       <c r="F149" s="5" t="n">
-        <v>5.306919</v>
+        <v>-5.306919</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/NGEX.xlsx
+++ b/output/pdf_financials_xlsx/NGEX.xlsx
@@ -735,19 +735,19 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.02568</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.24933</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-1.89994</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-3.621206</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-5.898385</v>
       </c>
     </row>
     <row r="13">
@@ -1183,19 +1183,19 @@
         <v>-5.306919</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-5.456734</v>
+        <v>-5.431054</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-32.415262</v>
+        <v>-32.165932</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-37.604891</v>
+        <v>-35.704951</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-63.047008</v>
+        <v>-59.425802</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-122.472475</v>
+        <v>-116.57409</v>
       </c>
     </row>
     <row r="28">
@@ -1239,19 +1239,19 @@
         <v>-5.303976</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-5.447923</v>
+        <v>-5.422243</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-32.402987</v>
+        <v>-32.153657</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-37.58766</v>
+        <v>-35.68772</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-62.988816</v>
+        <v>-59.36761</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-122.401804</v>
+        <v>-116.503419</v>
       </c>
     </row>
     <row r="30">
@@ -1380,19 +1380,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.255759</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>5.559454</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>21.000042</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>23.249241</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>59.502617</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>153.367759</v>
@@ -1436,19 +1436,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.255759</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>5.559454</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>21.000042</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>23.249241</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>15.229918</v>
+        <v>74.732535</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>198.552691</v>
@@ -1772,19 +1772,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.467997</v>
+        <v>0.212238</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>6.03934</v>
+        <v>0.479886</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>21.929654</v>
+        <v>0.929612</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>27.5498</v>
+        <v>4.300559</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>61.643578</v>
+        <v>2.140961</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>2.96721</v>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
@@ -10242,7 +10242,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">

--- a/output/pdf_financials_xlsx/NGEX.xlsx
+++ b/output/pdf_financials_xlsx/NGEX.xlsx
@@ -1551,7 +1551,7 @@
         <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.154683</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>0</v>
@@ -1560,13 +1560,13 @@
         <v>0</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.88567</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>1.474465</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.522833</v>
       </c>
     </row>
     <row r="41">
@@ -1579,7 +1579,7 @@
         <v>0</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0</v>
+        <v>0.154683</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0</v>
+        <v>0.88567</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0</v>
+        <v>1.474465</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0</v>
+        <v>0.522833</v>
       </c>
     </row>
     <row r="42">
@@ -1775,7 +1775,7 @@
         <v>0.212238</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.479886</v>
+        <v>0.325203</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.929612</v>
@@ -1784,13 +1784,13 @@
         <v>4.300559</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.140961</v>
+        <v>1.255291</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.96721</v>
+        <v>1.492745</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>176.498646</v>
+        <v>175.975813</v>
       </c>
     </row>
     <row r="49">
@@ -3562,7 +3562,7 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.035578</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -3571,10 +3571,10 @@
         <v>0</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.189419</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.215468</v>
       </c>
       <c r="H111" s="3" t="n">
         <v>0</v>
@@ -4224,7 +4224,7 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.035578</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -4233,10 +4233,10 @@
         <v>0</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.189419</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.215468</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>0</v>
@@ -4265,10 +4265,10 @@
         <v>-27.156678</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-27.087854</v>
+        <v>-27.277273</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-46.168594</v>
+        <v>-46.384062</v>
       </c>
       <c r="H135" s="3" t="n">
         <v>-93.49019199999999</v>
@@ -7012,7 +7012,11 @@
           <t>Acquisition of equipment 7</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -7859,7 +7863,11 @@
           <t>Acquisition of equipment 6</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -8214,7 +8222,11 @@
           <t>Acquisition of equipment 6</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -9457,7 +9469,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
